--- a/docs/REPOSITORY_INDEX.xlsx
+++ b/docs/REPOSITORY_INDEX.xlsx
@@ -1262,7 +1262,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Links locais dependem da máquina. GitHub aponta à main; arquivos novos aguardam publicação.</t>
+          <t>Links locais são relativos à planilha no repositório. GitHub aponta à main.</t>
         </is>
       </c>
       <c r="B4" s="1" t="n"/>
